--- a/artfynd/A 45174-2021 artfynd.xlsx
+++ b/artfynd/A 45174-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45174-2021 artfynd.xlsx
+++ b/artfynd/A 45174-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83326629</v>
+        <v>623082</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>VGL Träd ID: 21461, Vg</t>
+          <t>Horreds-Bosgården, träd 21125 (alm), Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346102.2849002739</v>
+        <v>346113</v>
       </c>
       <c r="R2" t="n">
-        <v>6357208.475086962</v>
+        <v>6356959</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,36 +738,16 @@
           <t>Horred</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>34A69901-295C-4C27-A1FC-79D482071771</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inventerat av Elisabeth Ryberg</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -785,6 +756,14 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # alm</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -794,68 +773,59 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Sjögren</t>
+          <t>Lena Smith</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83326661</v>
+        <v>732030</v>
       </c>
       <c r="B3" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>VGL Träd ID: 21120, Vg</t>
+          <t>Horreds-Bosgården, träd 21125 (alm), Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346147.6899185141</v>
+        <v>346113</v>
       </c>
       <c r="R3" t="n">
-        <v>6357062.500755122</v>
+        <v>6356959</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,31 +847,16 @@
           <t>Horred</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>C9055907-2D9B-483B-9673-0A7375794E62</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -910,6 +865,14 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # alm</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -919,68 +882,59 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Sjögren, Lena Smith</t>
+          <t>Lena Smith</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83326652</v>
+        <v>732031</v>
       </c>
       <c r="B4" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>2779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>VGL Träd ID: 21415, Vg</t>
+          <t>Horreds-Bosgården, träd 21124 (alm), Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346141.3441516052</v>
+        <v>346108</v>
       </c>
       <c r="R4" t="n">
-        <v>6357023.294258693</v>
+        <v>6356985</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,36 +956,16 @@
           <t>Horred</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>79ED4B9E-0F4C-47CB-A67C-4628F3CCE841</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Inventerat av Elisabeth Ryberg</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1040,6 +974,14 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # alm</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1049,26 +991,21 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Sjögren</t>
+          <t>Lena Smith</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>732035</v>
+        <v>732032</v>
       </c>
       <c r="B5" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,14 +1033,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, träd 21417 (ek), Vg</t>
+          <t>Horreds-Bosgården, träd 21415 (ask), Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346153.7652961744</v>
+        <v>346141</v>
       </c>
       <c r="R5" t="n">
-        <v>6357080.103631562</v>
+        <v>6357023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,19 +1070,9 @@
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1167,7 +1094,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # ek</t>
+          <t>1 substratenheter # ask</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,15 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>732030</v>
+        <v>732033</v>
       </c>
       <c r="B6" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,14 +1147,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, träd 21125 (alm), Vg</t>
+          <t>Horreds-Bosgården, träd 21119 (lind), Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346112.9396968464</v>
+        <v>346141</v>
       </c>
       <c r="R6" t="n">
-        <v>6356958.979457106</v>
+        <v>6357036</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,19 +1184,9 @@
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,7 +1203,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # alm</t>
+          <t>1 substratenheter # lind</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1313,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>732031</v>
+        <v>732034</v>
       </c>
       <c r="B7" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,14 +1256,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, träd 21124 (alm), Vg</t>
+          <t>Horreds-Bosgården, träd 21121 (alm), Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346107.9659278314</v>
+        <v>346140</v>
       </c>
       <c r="R7" t="n">
-        <v>6356985.103236576</v>
+        <v>6357075</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1386,19 +1293,9 @@
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,15 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>732032</v>
+        <v>732035</v>
       </c>
       <c r="B8" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,14 +1365,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, träd 21415 (ask), Vg</t>
+          <t>Horreds-Bosgården, träd 21417 (ek), Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346141.3441516052</v>
+        <v>346154</v>
       </c>
       <c r="R8" t="n">
-        <v>6357023.294258693</v>
+        <v>6357080</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1510,19 +1402,9 @@
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1544,7 +1426,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # ask</t>
+          <t>1 substratenheter # ek</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1566,15 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>732034</v>
+        <v>732036</v>
       </c>
       <c r="B9" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,14 +1479,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, träd 21121 (alm), Vg</t>
+          <t>Horreds-Bosgården, träd 21416 (alm), Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>346139.5060531003</v>
+        <v>346157</v>
       </c>
       <c r="R9" t="n">
-        <v>6357075.236037249</v>
+        <v>6357086</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,19 +1516,14 @@
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Inventerad av Elisabeth Ryberg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,7 +1551,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lena Smith</t>
+          <t>Via Lars Sjögren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1690,15 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>732033</v>
+        <v>732037</v>
       </c>
       <c r="B10" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,14 +1593,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, träd 21119 (lind), Vg</t>
+          <t>Horreds-Bosgården, träd 21123 (ek), Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346141.290099515</v>
+        <v>346138</v>
       </c>
       <c r="R10" t="n">
-        <v>6357036.264528641</v>
+        <v>6357089</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1763,19 +1630,9 @@
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,7 +1649,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # lind</t>
+          <t>1 substratenheter # ek</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1814,53 +1671,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>732037</v>
+        <v>83326629</v>
       </c>
       <c r="B11" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2779</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, träd 21123 (ek), Vg</t>
+          <t>VGL Träd ID: 21461, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>346138.4112995829</v>
+        <v>346102</v>
       </c>
       <c r="R11" t="n">
-        <v>6357089.325921047</v>
+        <v>6357208</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1882,24 +1738,24 @@
           <t>Horred</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>34A69901-295C-4C27-A1FC-79D482071771</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Inventerat av Elisabeth Ryberg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1910,14 +1766,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>1 substratenheter # ek</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1927,64 +1775,63 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lena Smith</t>
+          <t>Lars Sjögren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>623082</v>
+        <v>83326647</v>
       </c>
       <c r="B12" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>220785</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, träd 21125 (alm), Vg</t>
+          <t>VGL Träd ID: 21110, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>346112.9396968464</v>
+        <v>346131</v>
       </c>
       <c r="R12" t="n">
-        <v>6356958.979457106</v>
+        <v>6357250</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2006,26 +1853,21 @@
           <t>Horred</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>E8A36643-58A3-4FD0-B267-80CA1B858F9A</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2034,14 +1876,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>1 substratenheter # alm</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2051,64 +1885,63 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lena Smith</t>
+          <t>Lars Sjögren, Lena Smith</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>732036</v>
+        <v>83326652</v>
       </c>
       <c r="B13" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2779</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, träd 21416 (alm), Vg</t>
+          <t>VGL Träd ID: 21415, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>346156.7117399635</v>
+        <v>346141</v>
       </c>
       <c r="R13" t="n">
-        <v>6357086.476961588</v>
+        <v>6357023</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2130,29 +1963,24 @@
           <t>Horred</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>79ED4B9E-0F4C-47CB-A67C-4628F3CCE841</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2007-10-04</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Inventerad av Elisabeth Ryberg</t>
+          <t>Inventerat av Elisabeth Ryberg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,14 +1991,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>1 substratenheter # alm</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2180,73 +2000,63 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Lars Sjögren</t>
+          <t>Lars Sjögren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>75952934</v>
+        <v>83326656</v>
       </c>
       <c r="B14" t="n">
-        <v>9491</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101479</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>fallfälla</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Horred-Bosgården, Vg</t>
+          <t>VGL Träd ID: 21111, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>346142.9255288331</v>
+        <v>346142</v>
       </c>
       <c r="R14" t="n">
-        <v>6357022.154151178</v>
+        <v>6357248</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2268,24 +2078,19 @@
           <t>Horred</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1D2F36AC-8ADE-4041-8303-9E1B65D4ED4D</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2294,95 +2099,74 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Stenström</t>
+          <t>Lars Sjögren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Per Österman</t>
+          <t>Lars Sjögren, Lena Smith</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Läderbagge i Västra Götalands län, Länsstyrelsen</t>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95682411</v>
+        <v>83326661</v>
       </c>
       <c r="B15" t="n">
-        <v>100516</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, Vg</t>
+          <t>VGL Träd ID: 21120, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>346107.9659278314</v>
+        <v>346148</v>
       </c>
       <c r="R15" t="n">
-        <v>6356985.103236576</v>
+        <v>6357063</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2404,29 +2188,19 @@
           <t>Horred</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C9055907-2D9B-483B-9673-0A7375794E62</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Död i almsjuka. Stående. Omkrets 499 cm.</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2435,22 +2209,132 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars Sjögren, Lena Smith</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>95682411</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Horreds-Bosgården, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>346108</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6356985</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Horred</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Död i almsjuka. Stående. Omkrets 499 cm.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Jenny Pleym</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Jenny Pleym, Anita Sjöstrand</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
